--- a/buoi_08/so_yeu_ly_lich.xlsx
+++ b/buoi_08/so_yeu_ly_lich.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,6 +458,510 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NGUYỄN THỊ I</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>22 tháng 02 năm 2015</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Thành phố Đà Lạt, Tỉnh Lâm Đồng</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Phường 1, Thành phố Đà Lạt, Tỉnh Lâm Đồng</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Phường 1, Thành phố Đà Lạt, Tỉnh Lâm Đồng</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Toà Theta Residence, Thành phố Đà Lạt</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9890123456</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NGUYỄN VĂN B</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>05 tháng 06 năm 2015</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Phường Tân Định, Quận 01, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Phường Tân Định, Quận 01, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Toà Zeta Office</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>9876543210</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PHẠM VĂN H</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>10 tháng 09 năm 2014</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Thành phố Nha Trang, Tỉnh Khánh Hòa</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Phường Vĩnh Hòa, Thành phố Nha Trang, Tỉnh Khánh Hòa</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Phường Vĩnh Hòa, Thành phố Nha Trang, Tỉnh Khánh Hòa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Toà Eta Building, Thành phố Nha Trang</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>9789012345</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NGUYỄN THỊ C</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>07 tháng 06 năm 2020</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Phường Đa Kao, Quận 01, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Phường Đa Kao, Quận 01, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Toà nhà VNO</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>9876543210</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LÊ VĂN G</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>30 tháng 07 năm 2013</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Tỉnh Bà Rịa - Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Phường Phước Hưng, Thành phố Bà Rịa, Tỉnh Bà Rịa - Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Phường Phước Hưng, Thành phố Bà Rịa, Tỉnh Bà Rịa - Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Toà Zeta Complex, Thành phố Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>9678901234</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PHẠM THỊ D</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>15 tháng 11 năm 2015</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Thành phố Cần Thơ</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Phường An Khánh, Quận Ninh Kiều, Thành phố Cần Thơ</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Phường An Khánh, Quận Ninh Kiều, Thành phố Cần Thơ</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Toà Gamma Plaza, Quận Cái Răng, Cần Thơ</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>9345678901</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NGUYỄN VĂN E</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>03 tháng 01 năm 2014</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Thành phố Hải Phòng</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Phường Cát Dài, Quận Lê Chân, Thành phố Hải Phòng</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Phường Cát Dài, Quận Lê Chân, Thành phố Hải Phòng</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Toà Delta Center, Quận Hồng Bàng, Hải Phòng</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9456789012</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TRẦN THỊ F</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>25 tháng 04 năm 2015</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Thành phố Huế</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Phường Phú Nhuận, Thành phố Huế, Tỉnh Thừa Thiên Huế</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Phường Phú Nhuận, Thành phố Huế, Tỉnh Thừa Thiên Huế</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Toà Epsilon Tower, Thành phố Huế</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>9567890123</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TRẦN VĂN K</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>18 tháng 12 năm 2013</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Tỉnh Bình Dương</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Phường Phú Cường, Thành phố Thủ Dầu Một, Tỉnh Bình Dương</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Phường Phú Cường, Thành phố Thủ Dầu Một, Tỉnh Bình Dương</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Toà Iota Office, Thành phố Dĩ An, Bình Dương</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>9901234567</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LÊ VĂN C</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>20 tháng 08 năm 2013</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Thành phố Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Phường Hải Châu I, Quận Hải Châu, Thành phố Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Phường Hải Châu I, Quận Hải Châu, Thành phố Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Toà Beta Building, Quận Sơn Trà, Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>9234567890</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NGUYỄN VĂN A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>07 tháng 06 năm 2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Phường 04, Quận 03, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Phường 04, Quận 03, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Toà nhà Xuri</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1234567890</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TRẦN THỊ A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>12 tháng 03 năm 2014</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Thành phố Hà Nội</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Phường Hàng Bông, Quận Hoàn Kiếm, Thành phố Hà Nội</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Phường Hàng Bông, Quận Hoàn Kiếm, Thành phố Hà Nội</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Toà Alpha Tower, Quận Ba Đình, Hà Nội</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>9123456789</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
